--- a/Pertemuan 2/hasil_peramalan.xlsx
+++ b/Pertemuan 2/hasil_peramalan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>date</t>
   </si>
@@ -23,6 +23,9 @@
   </si>
   <si>
     <t>TMA_pred</t>
+  </si>
+  <si>
+    <t>TMA_naif</t>
   </si>
 </sst>
 </file>
@@ -369,13 +372,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C90"/>
+  <dimension ref="A1:D91"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1">
+    <row r="1" spans="1:4" s="2" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -385,19 +388,25 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="1">
         <v>45658</v>
       </c>
       <c r="B2">
-        <v>640</v>
+        <v>640.8</v>
       </c>
       <c r="C2">
-        <v>638.7076240264111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>633.409241384242</v>
+      </c>
+      <c r="D2">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="1">
         <v>45659</v>
       </c>
@@ -405,10 +414,13 @@
         <v>640</v>
       </c>
       <c r="C3">
-        <v>641.6819064659098</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>635.539182815005</v>
+      </c>
+      <c r="D3">
+        <v>640.8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>45660</v>
       </c>
@@ -416,10 +428,13 @@
         <v>640</v>
       </c>
       <c r="C4">
-        <v>641.6115808149948</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>634.6152127210314</v>
+      </c>
+      <c r="D4">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>45661</v>
       </c>
@@ -427,10 +442,13 @@
         <v>640</v>
       </c>
       <c r="C5">
-        <v>639.07327739382</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>638.6463801900923</v>
+      </c>
+      <c r="D5">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>45662</v>
       </c>
@@ -438,10 +456,13 @@
         <v>640</v>
       </c>
       <c r="C6">
-        <v>656.0404556023924</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>634.6746448503191</v>
+      </c>
+      <c r="D6">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>45663</v>
       </c>
@@ -449,76 +470,97 @@
         <v>640</v>
       </c>
       <c r="C7">
-        <v>645.7753058911524</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>648.2016746565763</v>
+      </c>
+      <c r="D7">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>45664</v>
       </c>
       <c r="B8">
-        <v>641.4583333333334</v>
+        <v>640</v>
       </c>
       <c r="C8">
-        <v>655.6076449383509</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>658.495138713477</v>
+      </c>
+      <c r="D8">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>45665</v>
       </c>
       <c r="B9">
-        <v>666.25</v>
+        <v>641.4583333333334</v>
       </c>
       <c r="C9">
-        <v>652.5695952397092</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>648.9574989479398</v>
+      </c>
+      <c r="D9">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>45666</v>
       </c>
       <c r="B10">
-        <v>642.5</v>
+        <v>666.25</v>
       </c>
       <c r="C10">
-        <v>642.5197208479933</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>662.1028439751578</v>
+      </c>
+      <c r="D10">
+        <v>641.4583333333334</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="1">
         <v>45667</v>
       </c>
       <c r="B11">
-        <v>637.5</v>
+        <v>642.5</v>
       </c>
       <c r="C11">
-        <v>647.9389158449455</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>654.6897728863887</v>
+      </c>
+      <c r="D11">
+        <v>666.25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12" s="1">
         <v>45668</v>
       </c>
       <c r="B12">
-        <v>634.5833333333334</v>
+        <v>637.5</v>
       </c>
       <c r="C12">
-        <v>640.1648091167713</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>643.9335116120302</v>
+      </c>
+      <c r="D12">
+        <v>642.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13" s="1">
         <v>45669</v>
       </c>
       <c r="B13">
-        <v>636.6666666666666</v>
+        <v>634.5833333333334</v>
       </c>
       <c r="C13">
-        <v>643.4004973014065</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>642.9826690516226</v>
+      </c>
+      <c r="D13">
+        <v>637.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14" s="1">
         <v>45670</v>
       </c>
@@ -526,43 +568,55 @@
         <v>636.6666666666666</v>
       </c>
       <c r="C14">
-        <v>656.4389009286621</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>633.0290111533898</v>
+      </c>
+      <c r="D14">
+        <v>634.5833333333334</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15" s="1">
         <v>45671</v>
       </c>
       <c r="B15">
-        <v>647.2916666666666</v>
+        <v>636.6666666666666</v>
       </c>
       <c r="C15">
-        <v>643.2367807867703</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>650.5328071612804</v>
+      </c>
+      <c r="D15">
+        <v>636.6666666666666</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" s="1">
         <v>45672</v>
       </c>
       <c r="B16">
-        <v>642.9166666666666</v>
+        <v>647.2916666666666</v>
       </c>
       <c r="C16">
-        <v>640.0757166198291</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>651.8636548877687</v>
+      </c>
+      <c r="D16">
+        <v>636.6666666666666</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17" s="1">
         <v>45673</v>
       </c>
       <c r="B17">
-        <v>640</v>
+        <v>642.9166666666666</v>
       </c>
       <c r="C17">
-        <v>654.7748155691285</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>632.3515266383051</v>
+      </c>
+      <c r="D17">
+        <v>647.2916666666666</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18" s="1">
         <v>45674</v>
       </c>
@@ -570,65 +624,83 @@
         <v>640</v>
       </c>
       <c r="C18">
-        <v>646.2164916055445</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>649.3451587165237</v>
+      </c>
+      <c r="D18">
+        <v>642.9166666666666</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19" s="1">
         <v>45675</v>
       </c>
       <c r="B19">
-        <v>640.4166666666666</v>
+        <v>640</v>
       </c>
       <c r="C19">
-        <v>650.9514186225806</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>657.7699645025591</v>
+      </c>
+      <c r="D19">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20" s="1">
         <v>45676</v>
       </c>
       <c r="B20">
-        <v>645</v>
+        <v>640.4166666666666</v>
       </c>
       <c r="C20">
-        <v>658.1312581970701</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>644.6196236611704</v>
+      </c>
+      <c r="D20">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21" s="1">
         <v>45677</v>
       </c>
       <c r="B21">
-        <v>642.0833333333334</v>
+        <v>645</v>
       </c>
       <c r="C21">
-        <v>657.7457079711374</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>659.6619750361463</v>
+      </c>
+      <c r="D21">
+        <v>640.4166666666666</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22" s="1">
         <v>45678</v>
       </c>
       <c r="B22">
-        <v>645.8333333333334</v>
+        <v>642.0833333333334</v>
       </c>
       <c r="C22">
-        <v>645.4123775116112</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>667.3143365364737</v>
+      </c>
+      <c r="D22">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23" s="1">
         <v>45679</v>
       </c>
       <c r="B23">
-        <v>640</v>
+        <v>645.8333333333334</v>
       </c>
       <c r="C23">
-        <v>662.2257876348091</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>651.4565259918014</v>
+      </c>
+      <c r="D23">
+        <v>642.0833333333334</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24" s="1">
         <v>45680</v>
       </c>
@@ -636,32 +708,41 @@
         <v>640</v>
       </c>
       <c r="C24">
-        <v>658.4035207007578</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>655.6743496619562</v>
+      </c>
+      <c r="D24">
+        <v>645.8333333333334</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25" s="1">
         <v>45681</v>
       </c>
       <c r="B25">
-        <v>642.5</v>
+        <v>640</v>
       </c>
       <c r="C25">
-        <v>645.3859222613153</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>674.9121717008434</v>
+      </c>
+      <c r="D25">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26" s="1">
         <v>45682</v>
       </c>
       <c r="B26">
-        <v>630</v>
+        <v>642.5</v>
       </c>
       <c r="C26">
-        <v>660.930745680174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>649.1357388749689</v>
+      </c>
+      <c r="D26">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27" s="1">
         <v>45683</v>
       </c>
@@ -669,98 +750,125 @@
         <v>630</v>
       </c>
       <c r="C27">
-        <v>640.5322791427586</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>651.943198986231</v>
+      </c>
+      <c r="D27">
+        <v>642.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28" s="1">
         <v>45684</v>
       </c>
       <c r="B28">
-        <v>646.25</v>
+        <v>630</v>
       </c>
       <c r="C28">
-        <v>661.4589855497227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>650.0737362146006</v>
+      </c>
+      <c r="D28">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29" s="1">
         <v>45685</v>
       </c>
       <c r="B29">
-        <v>692.2916666666666</v>
+        <v>646.25</v>
       </c>
       <c r="C29">
-        <v>686.4605462191092</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>639.1452991416811</v>
+      </c>
+      <c r="D29">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30" s="1">
         <v>45686</v>
       </c>
       <c r="B30">
-        <v>715.4166666666666</v>
+        <v>692.2916666666666</v>
       </c>
       <c r="C30">
-        <v>648.0865905014225</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>702.0161635292536</v>
+      </c>
+      <c r="D30">
+        <v>646.25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31" s="1">
         <v>45687</v>
       </c>
       <c r="B31">
-        <v>666.6304347826087</v>
+        <v>715.4166666666666</v>
       </c>
       <c r="C31">
-        <v>642.6036282453273</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>703.768136340513</v>
+      </c>
+      <c r="D31">
+        <v>692.2916666666666</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32" s="1">
         <v>45688</v>
       </c>
       <c r="B32">
-        <v>652.1739130434783</v>
+        <v>666.6304347826087</v>
       </c>
       <c r="C32">
-        <v>645.2396208970023</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>661.4603376401909</v>
+      </c>
+      <c r="D32">
+        <v>715.4166666666666</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33" s="1">
         <v>45689</v>
       </c>
       <c r="B33">
-        <v>650.8333333333334</v>
+        <v>652.1739130434783</v>
       </c>
       <c r="C33">
-        <v>641.4634843885633</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>661.9095749721183</v>
+      </c>
+      <c r="D33">
+        <v>666.6304347826087</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34" s="1">
         <v>45690</v>
       </c>
       <c r="B34">
-        <v>648.75</v>
+        <v>650.8333333333334</v>
       </c>
       <c r="C34">
-        <v>640.6781371406571</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>654.8415194165075</v>
+      </c>
+      <c r="D34">
+        <v>652.1739130434783</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35" s="1">
         <v>45691</v>
       </c>
       <c r="B35">
-        <v>640</v>
+        <v>648.75</v>
       </c>
       <c r="C35">
-        <v>641.991724258112</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>643.1292096225097</v>
+      </c>
+      <c r="D35">
+        <v>650.8333333333334</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36" s="1">
         <v>45692</v>
       </c>
@@ -768,10 +876,13 @@
         <v>640</v>
       </c>
       <c r="C36">
-        <v>644.5200792500249</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>639.8881630348457</v>
+      </c>
+      <c r="D36">
+        <v>648.75</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37" s="1">
         <v>45693</v>
       </c>
@@ -779,65 +890,83 @@
         <v>640</v>
       </c>
       <c r="C37">
-        <v>646.1181373254225</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>642.6555254284773</v>
+      </c>
+      <c r="D37">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38" s="1">
         <v>45694</v>
       </c>
       <c r="B38">
-        <v>643.3333333333334</v>
+        <v>640</v>
       </c>
       <c r="C38">
-        <v>646.3861014623312</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>647.6133761766075</v>
+      </c>
+      <c r="D38">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39" s="1">
         <v>45695</v>
       </c>
       <c r="B39">
-        <v>655</v>
+        <v>643.3333333333334</v>
       </c>
       <c r="C39">
-        <v>646.1466309175042</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>649.7807645730772</v>
+      </c>
+      <c r="D39">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40" s="1">
         <v>45696</v>
       </c>
       <c r="B40">
-        <v>635.8333333333334</v>
+        <v>655</v>
       </c>
       <c r="C40">
-        <v>650.3971884656108</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>648.1047790976946</v>
+      </c>
+      <c r="D40">
+        <v>643.3333333333334</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41" s="1">
         <v>45697</v>
       </c>
       <c r="B41">
-        <v>634.5833333333334</v>
+        <v>635.8333333333334</v>
       </c>
       <c r="C41">
-        <v>642.8844874825731</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>653.5706392718652</v>
+      </c>
+      <c r="D41">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42" s="1">
         <v>45698</v>
       </c>
       <c r="B42">
-        <v>630</v>
+        <v>634.5833333333334</v>
       </c>
       <c r="C42">
-        <v>640.907437573015</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>644.1156430372839</v>
+      </c>
+      <c r="D42">
+        <v>635.8333333333334</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43" s="1">
         <v>45699</v>
       </c>
@@ -845,10 +974,13 @@
         <v>630</v>
       </c>
       <c r="C43">
-        <v>640.3219888360957</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>628.92641815594</v>
+      </c>
+      <c r="D43">
+        <v>634.5833333333334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44" s="1">
         <v>45700</v>
       </c>
@@ -856,10 +988,13 @@
         <v>630</v>
       </c>
       <c r="C44">
-        <v>641.1127644632775</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>626.0564064918617</v>
+      </c>
+      <c r="D44">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45" s="1">
         <v>45701</v>
       </c>
@@ -867,10 +1002,13 @@
         <v>630</v>
       </c>
       <c r="C45">
-        <v>643.318206475904</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>624.0561052293911</v>
+      </c>
+      <c r="D45">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46" s="1">
         <v>45702</v>
       </c>
@@ -878,10 +1016,13 @@
         <v>630</v>
       </c>
       <c r="C46">
-        <v>643.6553662512313</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>627.5939224583122</v>
+      </c>
+      <c r="D46">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47" s="1">
         <v>45703</v>
       </c>
@@ -889,10 +1030,13 @@
         <v>630</v>
       </c>
       <c r="C47">
-        <v>653.4723284898923</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>629.5816329616753</v>
+      </c>
+      <c r="D47">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48" s="1">
         <v>45704</v>
       </c>
@@ -900,65 +1044,83 @@
         <v>630</v>
       </c>
       <c r="C48">
-        <v>656.008371886074</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
+        <v>638.8169511522229</v>
+      </c>
+      <c r="D48">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4">
       <c r="A49" s="1">
         <v>45705</v>
       </c>
       <c r="B49">
-        <v>637.0833333333334</v>
+        <v>630</v>
       </c>
       <c r="C49">
-        <v>652.2245469733663</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
+        <v>651.6980303503743</v>
+      </c>
+      <c r="D49">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4">
       <c r="A50" s="1">
         <v>45706</v>
       </c>
       <c r="B50">
-        <v>640</v>
+        <v>637.0833333333334</v>
       </c>
       <c r="C50">
-        <v>658.2895679288912</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
+        <v>645.2639887276238</v>
+      </c>
+      <c r="D50">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
       <c r="A51" s="1">
         <v>45707</v>
       </c>
       <c r="B51">
-        <v>642.2916666666666</v>
+        <v>640</v>
       </c>
       <c r="C51">
-        <v>643.634339380211</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3">
+        <v>648.2191058151739</v>
+      </c>
+      <c r="D51">
+        <v>637.0833333333334</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
       <c r="A52" s="1">
         <v>45708</v>
       </c>
       <c r="B52">
-        <v>642.5</v>
+        <v>642.2916666666666</v>
       </c>
       <c r="C52">
-        <v>645.3400351153707</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3">
+        <v>644.3001779089893</v>
+      </c>
+      <c r="D52">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
       <c r="A53" s="1">
         <v>45709</v>
       </c>
       <c r="B53">
-        <v>640</v>
+        <v>642.5</v>
       </c>
       <c r="C53">
-        <v>644.3317241436716</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3">
+        <v>628.402509039859</v>
+      </c>
+      <c r="D53">
+        <v>642.2916666666666</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
       <c r="A54" s="1">
         <v>45710</v>
       </c>
@@ -966,10 +1128,13 @@
         <v>640</v>
       </c>
       <c r="C54">
-        <v>652.9031648907998</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3">
+        <v>636.735592026546</v>
+      </c>
+      <c r="D54">
+        <v>642.5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
       <c r="A55" s="1">
         <v>45711</v>
       </c>
@@ -977,175 +1142,223 @@
         <v>640</v>
       </c>
       <c r="C55">
-        <v>652.2485205154618</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3">
+        <v>642.374836796016</v>
+      </c>
+      <c r="D55">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
       <c r="A56" s="1">
         <v>45712</v>
       </c>
       <c r="B56">
-        <v>669.7916666666666</v>
+        <v>640</v>
       </c>
       <c r="C56">
-        <v>646.9808335788908</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3">
+        <v>651.7603259706376</v>
+      </c>
+      <c r="D56">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
       <c r="A57" s="1">
         <v>45713</v>
       </c>
       <c r="B57">
-        <v>641.25</v>
+        <v>669.7916666666666</v>
       </c>
       <c r="C57">
-        <v>646.2569935651344</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3">
+        <v>642.0973176079086</v>
+      </c>
+      <c r="D57">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
       <c r="A58" s="1">
         <v>45714</v>
       </c>
       <c r="B58">
-        <v>645.4166666666666</v>
+        <v>641.25</v>
       </c>
       <c r="C58">
-        <v>652.2297536694347</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3">
+        <v>647.9103978845953</v>
+      </c>
+      <c r="D58">
+        <v>669.7916666666666</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
       <c r="A59" s="1">
         <v>45715</v>
       </c>
       <c r="B59">
-        <v>676.7391304347826</v>
+        <v>645.4166666666666</v>
       </c>
       <c r="C59">
-        <v>657.203021218801</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3">
+        <v>648.6977379457044</v>
+      </c>
+      <c r="D59">
+        <v>641.25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
       <c r="A60" s="1">
         <v>45716</v>
       </c>
       <c r="B60">
-        <v>707.9166666666666</v>
+        <v>676.7391304347826</v>
       </c>
       <c r="C60">
-        <v>652.6964863048336</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3">
+        <v>660.2566211702081</v>
+      </c>
+      <c r="D60">
+        <v>645.4166666666666</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
       <c r="A61" s="1">
         <v>45717</v>
       </c>
       <c r="B61">
-        <v>652.5</v>
+        <v>707.9166666666666</v>
       </c>
       <c r="C61">
-        <v>666.9265925937409</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3">
+        <v>672.3780689329211</v>
+      </c>
+      <c r="D61">
+        <v>676.7391304347826</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
       <c r="A62" s="1">
         <v>45718</v>
       </c>
       <c r="B62">
-        <v>746.4583333333334</v>
+        <v>652.5</v>
       </c>
       <c r="C62">
-        <v>681.2105177125293</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3">
+        <v>693.7087057202173</v>
+      </c>
+      <c r="D62">
+        <v>707.9166666666666</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
       <c r="A63" s="1">
         <v>45719</v>
       </c>
       <c r="B63">
-        <v>796.0416666666666</v>
+        <v>746.4583333333334</v>
       </c>
       <c r="C63">
-        <v>650.4173286038022</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3">
+        <v>711.7941001491829</v>
+      </c>
+      <c r="D63">
+        <v>652.5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
       <c r="A64" s="1">
         <v>45720</v>
       </c>
       <c r="B64">
-        <v>706.25</v>
+        <v>796.0416666666666</v>
       </c>
       <c r="C64">
-        <v>642.7124175140464</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3">
+        <v>725.7688133624953</v>
+      </c>
+      <c r="D64">
+        <v>746.4583333333334</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
       <c r="A65" s="1">
         <v>45721</v>
       </c>
       <c r="B65">
-        <v>670</v>
+        <v>706.25</v>
       </c>
       <c r="C65">
-        <v>644.5872581431179</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3">
+        <v>709.8432400625575</v>
+      </c>
+      <c r="D65">
+        <v>796.0416666666666</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
       <c r="A66" s="1">
         <v>45722</v>
       </c>
       <c r="B66">
-        <v>681.6666666666666</v>
+        <v>670</v>
       </c>
       <c r="C66">
-        <v>651.9593078243255</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3">
+        <v>690.4071919559602</v>
+      </c>
+      <c r="D66">
+        <v>706.25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
       <c r="A67" s="1">
         <v>45723</v>
       </c>
       <c r="B67">
-        <v>658.75</v>
+        <v>681.6666666666666</v>
       </c>
       <c r="C67">
-        <v>643.83153449979</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3">
+        <v>686.6815345968593</v>
+      </c>
+      <c r="D67">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
       <c r="A68" s="1">
         <v>45724</v>
       </c>
       <c r="B68">
-        <v>683.9583333333334</v>
+        <v>658.75</v>
       </c>
       <c r="C68">
-        <v>643.5074915080071</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3">
+        <v>682.0992330817123</v>
+      </c>
+      <c r="D68">
+        <v>681.6666666666666</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
       <c r="A69" s="1">
         <v>45725</v>
       </c>
       <c r="B69">
-        <v>672.9166666666666</v>
+        <v>683.9583333333334</v>
       </c>
       <c r="C69">
-        <v>643.106564473537</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3">
+        <v>656.0102340222004</v>
+      </c>
+      <c r="D69">
+        <v>658.75</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
       <c r="A70" s="1">
         <v>45726</v>
       </c>
       <c r="B70">
-        <v>660</v>
+        <v>672.9166666666666</v>
       </c>
       <c r="C70">
-        <v>642.1213187146441</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3">
+        <v>667.8993986299311</v>
+      </c>
+      <c r="D70">
+        <v>683.9583333333334</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
       <c r="A71" s="1">
         <v>45727</v>
       </c>
@@ -1153,10 +1366,13 @@
         <v>660</v>
       </c>
       <c r="C71">
-        <v>643.1581232784249</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3">
+        <v>666.2974153443129</v>
+      </c>
+      <c r="D71">
+        <v>672.9166666666666</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
       <c r="A72" s="1">
         <v>45728</v>
       </c>
@@ -1164,10 +1380,13 @@
         <v>660</v>
       </c>
       <c r="C72">
-        <v>645.6095942276506</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
+        <v>663.5968841560879</v>
+      </c>
+      <c r="D72">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
       <c r="A73" s="1">
         <v>45729</v>
       </c>
@@ -1175,10 +1394,13 @@
         <v>660</v>
       </c>
       <c r="C73">
-        <v>651.9437093325807</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
+        <v>664.5385631176325</v>
+      </c>
+      <c r="D73">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
       <c r="A74" s="1">
         <v>45730</v>
       </c>
@@ -1186,10 +1408,13 @@
         <v>660</v>
       </c>
       <c r="C74">
-        <v>649.7821377205734</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
+        <v>663.5079501639885</v>
+      </c>
+      <c r="D74">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
       <c r="A75" s="1">
         <v>45731</v>
       </c>
@@ -1197,54 +1422,69 @@
         <v>660</v>
       </c>
       <c r="C75">
-        <v>643.5995306760245</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
+        <v>665.3516589647295</v>
+      </c>
+      <c r="D75">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
       <c r="A76" s="1">
         <v>45732</v>
       </c>
       <c r="B76">
-        <v>660.8333333333334</v>
+        <v>660</v>
       </c>
       <c r="C76">
-        <v>649.4108342906816</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
+        <v>654.0367799707276</v>
+      </c>
+      <c r="D76">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
       <c r="A77" s="1">
         <v>45733</v>
       </c>
       <c r="B77">
-        <v>730.8333333333334</v>
+        <v>660.8333333333334</v>
       </c>
       <c r="C77">
-        <v>645.9729875700664</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
+        <v>652.854622760107</v>
+      </c>
+      <c r="D77">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
       <c r="A78" s="1">
         <v>45734</v>
       </c>
       <c r="B78">
-        <v>665</v>
+        <v>730.8333333333334</v>
       </c>
       <c r="C78">
-        <v>645.3337200032659</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
+        <v>659.4832251142439</v>
+      </c>
+      <c r="D78">
+        <v>660.8333333333334</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
       <c r="A79" s="1">
         <v>45735</v>
       </c>
       <c r="B79">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="C79">
-        <v>643.2105904126021</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
+        <v>679.4550285019513</v>
+      </c>
+      <c r="D79">
+        <v>730.8333333333334</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
       <c r="A80" s="1">
         <v>45736</v>
       </c>
@@ -1252,10 +1492,13 @@
         <v>660</v>
       </c>
       <c r="C80">
-        <v>642.8711706122817</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
+        <v>661.3157843648378</v>
+      </c>
+      <c r="D80">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
       <c r="A81" s="1">
         <v>45737</v>
       </c>
@@ -1263,10 +1506,13 @@
         <v>660</v>
       </c>
       <c r="C81">
-        <v>649.1053364617185</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3">
+        <v>651.7908532290413</v>
+      </c>
+      <c r="D81">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
       <c r="A82" s="1">
         <v>45738</v>
       </c>
@@ -1274,10 +1520,13 @@
         <v>660</v>
       </c>
       <c r="C82">
-        <v>645.7674389965966</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3">
+        <v>658.0816387597993</v>
+      </c>
+      <c r="D82">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
       <c r="A83" s="1">
         <v>45739</v>
       </c>
@@ -1285,65 +1534,83 @@
         <v>660</v>
       </c>
       <c r="C83">
-        <v>644.6053599395231</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3">
+        <v>655.3504606462976</v>
+      </c>
+      <c r="D83">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
       <c r="A84" s="1">
         <v>45740</v>
       </c>
       <c r="B84">
-        <v>653.75</v>
+        <v>660</v>
       </c>
       <c r="C84">
-        <v>643.8353895001543</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
+        <v>650.451386541332</v>
+      </c>
+      <c r="D84">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
       <c r="A85" s="1">
         <v>45741</v>
       </c>
       <c r="B85">
-        <v>650</v>
+        <v>653.75</v>
       </c>
       <c r="C85">
-        <v>644.5877231059925</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>649.807127336352</v>
+      </c>
+      <c r="D85">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
       <c r="A86" s="1">
         <v>45742</v>
       </c>
       <c r="B86">
-        <v>651.25</v>
+        <v>650</v>
       </c>
       <c r="C86">
-        <v>644.9556364983946</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3">
+        <v>649.3016460986871</v>
+      </c>
+      <c r="D86">
+        <v>653.75</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
       <c r="A87" s="1">
         <v>45743</v>
       </c>
       <c r="B87">
-        <v>654.1666666666666</v>
+        <v>651.25</v>
       </c>
       <c r="C87">
-        <v>646.9227379786907</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3">
+        <v>648.6188009682323</v>
+      </c>
+      <c r="D87">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
       <c r="A88" s="1">
         <v>45744</v>
       </c>
       <c r="B88">
-        <v>650</v>
+        <v>654.1666666666666</v>
       </c>
       <c r="C88">
-        <v>644.0845867910358</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
+        <v>646.0760253431765</v>
+      </c>
+      <c r="D88">
+        <v>651.25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
       <c r="A89" s="1">
         <v>45745</v>
       </c>
@@ -1351,18 +1618,38 @@
         <v>650</v>
       </c>
       <c r="C89">
-        <v>644.9906884822484</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
+        <v>645.6074500994634</v>
+      </c>
+      <c r="D89">
+        <v>654.1666666666666</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
       <c r="A90" s="1">
         <v>45746</v>
       </c>
       <c r="B90">
+        <v>650</v>
+      </c>
+      <c r="C90">
+        <v>640.9635295744423</v>
+      </c>
+      <c r="D90">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4">
+      <c r="A91" s="1">
+        <v>45747</v>
+      </c>
+      <c r="B91">
         <v>650.2173913043479</v>
       </c>
-      <c r="C90">
-        <v>649.0797895407118</v>
+      <c r="C91">
+        <v>646.6567012013405</v>
+      </c>
+      <c r="D91">
+        <v>650</v>
       </c>
     </row>
   </sheetData>
